--- a/Data IKM Magang.xlsx
+++ b/Data IKM Magang.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MAGANG\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MAGANG\TUGAS\WEBSITE-DISPUSIP NEW\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0701B4A0-0E0E-4EF3-8A64-B9FB3B005C35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEECAFAC-9843-4BBA-9011-04A3636555CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{68260FC1-1412-47ED-B423-419084787DC8}"/>
   </bookViews>
@@ -413,7 +413,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -429,6 +429,9 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -764,12 +767,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A0DF6E50-6B51-46D6-8767-B2BAD62C16F4}">
-  <dimension ref="A1:M39"/>
+  <dimension ref="A1:M87"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="4.36328125" customWidth="1"/>
     <col min="3" max="3" width="14" customWidth="1"/>
     <col min="4" max="4" width="17.453125" customWidth="1"/>
+    <col min="5" max="5" width="14.08984375" customWidth="1"/>
     <col min="6" max="6" width="10.81640625" customWidth="1"/>
     <col min="7" max="7" width="16.08984375" customWidth="1"/>
     <col min="8" max="8" width="21.453125" customWidth="1"/>
@@ -2341,7 +2345,267 @@
     <row r="39" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A39" s="1"/>
     </row>
+    <row r="44" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A44" s="1"/>
+      <c r="B44" s="1"/>
+      <c r="C44" s="6"/>
+      <c r="D44" s="1"/>
+      <c r="E44" s="1"/>
+    </row>
+    <row r="45" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A45" s="1"/>
+      <c r="B45" s="2"/>
+      <c r="C45" s="4"/>
+      <c r="D45" s="1"/>
+    </row>
+    <row r="46" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A46" s="1"/>
+      <c r="B46" s="2"/>
+      <c r="C46" s="4"/>
+      <c r="D46" s="1"/>
+    </row>
+    <row r="47" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A47" s="1"/>
+      <c r="B47" s="2"/>
+      <c r="C47" s="4"/>
+      <c r="D47" s="1"/>
+    </row>
+    <row r="48" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A48" s="1"/>
+      <c r="B48" s="2"/>
+      <c r="C48" s="4"/>
+      <c r="D48" s="1"/>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A49" s="1"/>
+      <c r="B49" s="2"/>
+      <c r="C49" s="4"/>
+      <c r="D49" s="1"/>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A50" s="1"/>
+      <c r="B50" s="2"/>
+      <c r="C50" s="4"/>
+      <c r="D50" s="1"/>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A51" s="1"/>
+      <c r="B51" s="2"/>
+      <c r="C51" s="4"/>
+      <c r="D51" s="1"/>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A52" s="1"/>
+      <c r="B52" s="2"/>
+      <c r="C52" s="4"/>
+      <c r="D52" s="1"/>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A53" s="1"/>
+      <c r="B53" s="2"/>
+      <c r="C53" s="4"/>
+      <c r="D53" s="1"/>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A54" s="1"/>
+      <c r="B54" s="2"/>
+      <c r="C54" s="4"/>
+      <c r="D54" s="1"/>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A55" s="1"/>
+      <c r="B55" s="2"/>
+      <c r="C55" s="4"/>
+      <c r="D55" s="1"/>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A56" s="1"/>
+      <c r="B56" s="2"/>
+      <c r="C56" s="4"/>
+      <c r="D56" s="1"/>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A57" s="1"/>
+      <c r="B57" s="2"/>
+      <c r="C57" s="4"/>
+      <c r="D57" s="1"/>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A58" s="1"/>
+      <c r="B58" s="2"/>
+      <c r="C58" s="4"/>
+      <c r="D58" s="1"/>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A59" s="1"/>
+      <c r="B59" s="2"/>
+      <c r="C59" s="4"/>
+      <c r="D59" s="1"/>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A60" s="1"/>
+      <c r="B60" s="2"/>
+      <c r="C60" s="4"/>
+      <c r="D60" s="1"/>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A61" s="1"/>
+      <c r="B61" s="2"/>
+      <c r="C61" s="4"/>
+      <c r="D61" s="1"/>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A62" s="1"/>
+      <c r="B62" s="2"/>
+      <c r="C62" s="4"/>
+      <c r="D62" s="1"/>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A63" s="1"/>
+      <c r="B63" s="2"/>
+      <c r="C63" s="4"/>
+      <c r="D63" s="1"/>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A64" s="1"/>
+      <c r="B64" s="2"/>
+      <c r="C64" s="4"/>
+      <c r="D64" s="1"/>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A65" s="1"/>
+      <c r="B65" s="2"/>
+      <c r="C65" s="4"/>
+      <c r="D65" s="1"/>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A66" s="1"/>
+      <c r="B66" s="2"/>
+      <c r="C66" s="4"/>
+      <c r="D66" s="1"/>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A67" s="1"/>
+      <c r="B67" s="2"/>
+      <c r="C67" s="4"/>
+      <c r="D67" s="1"/>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A68" s="1"/>
+      <c r="B68" s="2"/>
+      <c r="C68" s="4"/>
+      <c r="D68" s="1"/>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A69" s="1"/>
+      <c r="B69" s="2"/>
+      <c r="C69" s="4"/>
+      <c r="D69" s="1"/>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A70" s="1"/>
+      <c r="B70" s="2"/>
+      <c r="C70" s="4"/>
+      <c r="D70" s="1"/>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A71" s="1"/>
+      <c r="B71" s="2"/>
+      <c r="C71" s="4"/>
+      <c r="D71" s="1"/>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A72" s="1"/>
+      <c r="B72" s="2"/>
+      <c r="C72" s="4"/>
+      <c r="D72" s="1"/>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A73" s="1"/>
+      <c r="B73" s="2"/>
+      <c r="C73" s="4"/>
+      <c r="D73" s="1"/>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A74" s="1"/>
+      <c r="B74" s="2"/>
+      <c r="C74" s="4"/>
+      <c r="D74" s="1"/>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A75" s="1"/>
+      <c r="B75" s="2"/>
+      <c r="C75" s="4"/>
+      <c r="D75" s="1"/>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A76" s="1"/>
+      <c r="B76" s="2"/>
+      <c r="C76" s="4"/>
+      <c r="D76" s="1"/>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A77" s="1"/>
+      <c r="B77" s="2"/>
+      <c r="C77" s="4"/>
+      <c r="D77" s="1"/>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A78" s="1"/>
+      <c r="B78" s="2"/>
+      <c r="C78" s="4"/>
+      <c r="D78" s="1"/>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A79" s="1"/>
+      <c r="B79" s="2"/>
+      <c r="C79" s="4"/>
+      <c r="D79" s="1"/>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A80" s="1"/>
+      <c r="B80" s="2"/>
+      <c r="C80" s="4"/>
+      <c r="D80" s="1"/>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A81" s="1"/>
+      <c r="B81" s="2"/>
+      <c r="C81" s="4"/>
+      <c r="D81" s="1"/>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A82" s="1"/>
+      <c r="B82" s="2"/>
+      <c r="E82" s="1"/>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A83" s="1"/>
+      <c r="B83" s="2"/>
+      <c r="E83" s="1"/>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A84" s="1"/>
+      <c r="B84" s="2"/>
+      <c r="E84" s="1"/>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A85" s="1"/>
+      <c r="B85" s="2"/>
+      <c r="E85" s="1"/>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A86" s="1"/>
+      <c r="B86" s="2"/>
+      <c r="E86" s="1"/>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A87" s="1"/>
+      <c r="B87" s="2"/>
+      <c r="E87" s="1"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>